--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -57,7 +57,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F4FA"/>
+        <fgColor rgb="00EEF3FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -195,16 +195,11 @@
   <commentList>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>القيم المقبولة:
-الرتبة 10
-الرتبة 11
-الرتبة 12
-الرتبة 13
-الرتبة 14
-الرتبة 15
-الرتبة 16
-الرتبة 17
-أعلى من 17</t>
+        <t>الأسلاك:
+• أساتذة محاضرون → صيغة 1
+• أساتذة مساعدون → صيغة 2
+• طلبة دكتوراه → صيغة 3
+• إداريون وتقنيون → صيغة 4</t>
       </text>
     </comment>
   </commentList>
@@ -500,17 +495,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -531,25 +527,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>الرتبة_الوظيفية</t>
+          <t>السلك</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>الرتبة</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الصنف</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>سنوات_الخدمة</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>المنصب</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>الدور</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>الحالة</t>
         </is>
@@ -558,7 +559,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>اسم الدخول — حروف صغيرة</t>
+          <t>حروف صغيرة بدون مسافات</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -573,25 +574,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الرتبة 10 / 11 / ... / 17 / أعلى من 17</t>
+          <t>أساتذة محاضرون / أساتذة مساعدون / طلبة دكتوراه / إداريون وتقنيون</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>المنصب: مهندس / أستاذ محاضر أ / متصرف...</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>رقم الصنف: 10، 11، 12...</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>عدد سنوات الخدمة (رقم)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>اسم المنصب</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>موظف / لجنة / إدارة</t>
-        </is>
-      </c>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>مترشح / لجنة / إدارة</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>active / inactive</t>
         </is>
@@ -610,28 +616,31 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>محمد بن علي</t>
+          <t>أ.د. محمد بن علي</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>الرتبة 14</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>مكلف بالمكتبة</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>موظف</t>
-        </is>
+          <t>أساتذة محاضرون</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>أستاذ التعليم العالي</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>مترشح</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -650,28 +659,31 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>سارة معمري</t>
+          <t>أ. سارة معمري</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>الرتبة 12</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>سكرتيرة إدارية</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>موظف</t>
-        </is>
+          <t>أساتذة محاضرون</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>أستاذ محاضر قسم أ</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>8</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>مترشح</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -680,38 +692,41 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>cherif</t>
+          <t>bouzid</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Bjb@5678</t>
+          <t>Bjb@2345</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>أحمد شريف</t>
+          <t>أ. كريم بوزيد</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>الرتبة 17</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>رئيس مصلحة الموارد</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>موظف</t>
-        </is>
+          <t>أساتذة محاضرون</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>أستاذ محاضر قسم ب</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>مترشح</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -720,38 +735,41 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>boukhari</t>
+          <t>cherif</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Bjb@9012</t>
+          <t>Bjb@5678</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>فاطمة بوخاري</t>
+          <t>أ. أحمد شريف</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>الرتبة 15</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>مهندس تطبيقي</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>موظف</t>
-        </is>
+          <t>أساتذة مساعدون</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>أستاذ مساعد قسم أ</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>مترشح</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -760,38 +778,41 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>hamidi</t>
+          <t>boukhari</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Bjb@3456</t>
+          <t>Bjb@9012</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>كريم حميدي</t>
+          <t>أ. فاطمة بوخاري</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>الرتبة 11</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>تقني سامي</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>موظف</t>
-        </is>
+          <t>أساتذة مساعدون</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>أستاذ مساعد قسم ب</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>مترشح</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -800,38 +821,41 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>comite1</t>
+          <t>hamidi</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Com@2026</t>
+          <t>Bjb@3456</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>لجنة الانتقاء</t>
+          <t>كريم حميدي</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>الرتبة 17</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>رئيس اللجنة</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>لجنة</t>
-        </is>
+          <t>طلبة دكتوراه</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>طالب دكتوراه</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>مترشح</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -840,44 +864,273 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>kerroum</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Bjb@7890</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>نور الهدى كروم</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>طلبة دكتوراه</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>طالب دكتوراه</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>مترشح</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ferhat</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Bjb@1111</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>سليم فرحات</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>إداريون وتقنيون</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>مهندس رئيس</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>مترشح</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>bensalem</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Bjb@2222</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>أمينة بن سالم</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>إداريون وتقنيون</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>متصرف</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>مترشح</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>meziani</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Bjb@3333</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>يوسف مزياني</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>إداريون وتقنيون</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>تقني سامي</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>مترشح</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>comite1</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Com@2026</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>لجنة الانتقاء</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>أساتذة محاضرون</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>أستاذ التعليم العالي</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>لجنة</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Adm@2026</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>مدير المنصة</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>أعلى من 17</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>المدير</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>إداريون وتقنيون</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>مدير</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>إدارة</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="D3:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="اختر من القائمة فقط" prompt="اختر السلك" type="list">
+      <formula1>"أساتذة محاضرون,أساتذة مساعدون,طلبة دكتوراه,إداريون وتقنيون"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H3:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"مترشح,لجنة,إدارة"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I3:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"active,inactive"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -507,6 +507,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -555,6 +556,11 @@
           <t>الحالة</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>نقاط_الرتبة</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -602,6 +608,11 @@
           <t>active / inactive</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>النقطة الافتراضية للرتبة (يحددها المسؤول)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -645,6 +656,9 @@
           <t>active</t>
         </is>
       </c>
+      <c r="J3" s="3" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -688,6 +702,9 @@
           <t>active</t>
         </is>
       </c>
+      <c r="J4" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -731,6 +748,9 @@
           <t>active</t>
         </is>
       </c>
+      <c r="J5" s="3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -774,6 +794,9 @@
           <t>active</t>
         </is>
       </c>
+      <c r="J6" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -817,6 +840,9 @@
           <t>active</t>
         </is>
       </c>
+      <c r="J7" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -860,6 +886,9 @@
           <t>active</t>
         </is>
       </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -903,6 +932,9 @@
           <t>active</t>
         </is>
       </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -946,6 +978,9 @@
           <t>active</t>
         </is>
       </c>
+      <c r="J10" s="4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -989,6 +1024,9 @@
           <t>active</t>
         </is>
       </c>
+      <c r="J11" s="3" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -1032,6 +1070,9 @@
           <t>active</t>
         </is>
       </c>
+      <c r="J12" s="4" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -1075,6 +1116,9 @@
           <t>active</t>
         </is>
       </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1117,6 +1161,9 @@
         <is>
           <t>active</t>
         </is>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MAS\Desktop\Nouveau dossier (7)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7288219-D89D-446E-B902-1D8EE4A8B885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEB972E-D5AF-49B6-81A8-9B63F85A4DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المستخدمون" sheetId="1" r:id="rId1"/>
